--- a/DataStatistic/statistic_results.xlsx
+++ b/DataStatistic/statistic_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Total alignment</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Average Proportion</t>
         </is>
       </c>
@@ -511,6 +516,9 @@
         <v>1357</v>
       </c>
       <c r="J2" t="n">
+        <v>198</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.2007</v>
       </c>
     </row>
@@ -545,6 +553,9 @@
         <v>3609</v>
       </c>
       <c r="J3" t="n">
+        <v>17170</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.2378</v>
       </c>
     </row>
@@ -579,6 +590,9 @@
         <v>3348</v>
       </c>
       <c r="J4" t="n">
+        <v>9024</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.2558</v>
       </c>
     </row>
@@ -613,6 +627,9 @@
         <v>3424</v>
       </c>
       <c r="J5" t="n">
+        <v>8371</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.2633</v>
       </c>
     </row>
@@ -647,6 +664,9 @@
         <v>3313</v>
       </c>
       <c r="J6" t="n">
+        <v>8050</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.2648</v>
       </c>
     </row>
@@ -681,6 +701,9 @@
         <v>2741</v>
       </c>
       <c r="J7" t="n">
+        <v>4217</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.2239</v>
       </c>
     </row>
@@ -715,6 +738,9 @@
         <v>1334</v>
       </c>
       <c r="J8" t="n">
+        <v>631</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.2334</v>
       </c>
     </row>
@@ -749,6 +775,9 @@
         <v>2406</v>
       </c>
       <c r="J9" t="n">
+        <v>2189</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -783,6 +812,9 @@
         <v>1817</v>
       </c>
       <c r="J10" t="n">
+        <v>1253</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -817,6 +849,9 @@
         <v>4161</v>
       </c>
       <c r="J11" t="n">
+        <v>1701</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.8507</v>
       </c>
     </row>
@@ -851,6 +886,9 @@
         <v>2910</v>
       </c>
       <c r="J12" t="n">
+        <v>3617</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.2441</v>
       </c>
     </row>
@@ -885,6 +923,9 @@
         <v>986</v>
       </c>
       <c r="J13" t="n">
+        <v>157</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -919,6 +960,9 @@
         <v>3880</v>
       </c>
       <c r="J14" t="n">
+        <v>25124</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -947,12 +991,15 @@
         <v>8490</v>
       </c>
       <c r="H15" t="n">
-        <v>33808</v>
+        <v>1898969</v>
       </c>
       <c r="I15" t="n">
         <v>7303</v>
       </c>
       <c r="J15" t="n">
+        <v>81702</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.2856</v>
       </c>
     </row>

--- a/DataStatistic/statistic_results.xlsx
+++ b/DataStatistic/statistic_results.xlsx
@@ -501,7 +501,7 @@
         <v>18.14</v>
       </c>
       <c r="E2" t="n">
-        <v>91.59999999999999</v>
+        <v>23.24</v>
       </c>
       <c r="F2" t="n">
         <v>7192</v>
@@ -519,7 +519,7 @@
         <v>198</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2007</v>
+        <v>0.7849</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>21.6</v>
       </c>
       <c r="E3" t="n">
-        <v>103.95</v>
+        <v>26.72</v>
       </c>
       <c r="F3" t="n">
         <v>360475</v>
@@ -556,7 +556,7 @@
         <v>17170</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2378</v>
+        <v>0.9085</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>19.07</v>
       </c>
       <c r="E4" t="n">
-        <v>77.72</v>
+        <v>20.69</v>
       </c>
       <c r="F4" t="n">
         <v>168755</v>
@@ -593,7 +593,7 @@
         <v>9024</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2558</v>
+        <v>0.9452</v>
       </c>
     </row>
     <row r="5">
@@ -612,7 +612,7 @@
         <v>19.44</v>
       </c>
       <c r="E5" t="n">
-        <v>81.29000000000001</v>
+        <v>21.51</v>
       </c>
       <c r="F5" t="n">
         <v>165826</v>
@@ -630,7 +630,7 @@
         <v>8371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2633</v>
+        <v>0.979</v>
       </c>
     </row>
     <row r="6">
@@ -649,7 +649,7 @@
         <v>21.16</v>
       </c>
       <c r="E6" t="n">
-        <v>83.31</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>170058</v>
@@ -667,7 +667,7 @@
         <v>8050</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2648</v>
+        <v>0.9921</v>
       </c>
     </row>
     <row r="7">
@@ -686,7 +686,7 @@
         <v>19.39</v>
       </c>
       <c r="E7" t="n">
-        <v>125.6</v>
+        <v>31.39</v>
       </c>
       <c r="F7" t="n">
         <v>109414</v>
@@ -704,7 +704,7 @@
         <v>4217</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2239</v>
+        <v>0.8859</v>
       </c>
     </row>
     <row r="8">
@@ -723,7 +723,7 @@
         <v>11.32</v>
       </c>
       <c r="E8" t="n">
-        <v>49.41</v>
+        <v>13.2</v>
       </c>
       <c r="F8" t="n">
         <v>6772</v>
@@ -741,7 +741,7 @@
         <v>631</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2334</v>
+        <v>0.8591</v>
       </c>
     </row>
     <row r="9">
@@ -760,7 +760,7 @@
         <v>6.68</v>
       </c>
       <c r="E9" t="n">
-        <v>97.34999999999999</v>
+        <v>24.98</v>
       </c>
       <c r="F9" t="n">
         <v>34177</v>
@@ -778,7 +778,7 @@
         <v>2189</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2377</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="10">
@@ -797,7 +797,7 @@
         <v>14.52</v>
       </c>
       <c r="E10" t="n">
-        <v>71.43000000000001</v>
+        <v>18.87</v>
       </c>
       <c r="F10" t="n">
         <v>16433</v>
@@ -815,7 +815,7 @@
         <v>1253</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2061</v>
+        <v>0.7611</v>
       </c>
     </row>
     <row r="11">
@@ -834,7 +834,7 @@
         <v>12.8</v>
       </c>
       <c r="E11" t="n">
-        <v>19.4</v>
+        <v>5.8</v>
       </c>
       <c r="F11" t="n">
         <v>21185</v>
@@ -852,7 +852,7 @@
         <v>1701</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8507</v>
+        <v>2.4904</v>
       </c>
     </row>
     <row r="12">
@@ -871,7 +871,7 @@
         <v>16.7</v>
       </c>
       <c r="E12" t="n">
-        <v>87.66</v>
+        <v>23.03</v>
       </c>
       <c r="F12" t="n">
         <v>54030</v>
@@ -889,7 +889,7 @@
         <v>3617</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2441</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="13">
@@ -908,7 +908,7 @@
         <v>34.19</v>
       </c>
       <c r="E13" t="n">
-        <v>133.19</v>
+        <v>33.79</v>
       </c>
       <c r="F13" t="n">
         <v>5139</v>
@@ -926,7 +926,7 @@
         <v>157</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2589</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="14">
@@ -942,10 +942,10 @@
         <v>26452</v>
       </c>
       <c r="D14" t="n">
-        <v>19.15</v>
+        <v>18.45</v>
       </c>
       <c r="E14" t="n">
-        <v>102.25</v>
+        <v>26.77</v>
       </c>
       <c r="F14" t="n">
         <v>475534</v>
@@ -963,7 +963,7 @@
         <v>25124</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2351</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="15">
@@ -979,10 +979,10 @@
         <v>94376</v>
       </c>
       <c r="D15" t="n">
-        <v>18.78</v>
+        <v>18.56</v>
       </c>
       <c r="E15" t="n">
-        <v>90.66</v>
+        <v>23.67</v>
       </c>
       <c r="F15" t="n">
         <v>1594990</v>
@@ -1000,7 +1000,7 @@
         <v>81702</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2856</v>
+        <v>1.0054</v>
       </c>
     </row>
   </sheetData>

--- a/DataStatistic/statistic_results.xlsx
+++ b/DataStatistic/statistic_results.xlsx
@@ -510,7 +510,7 @@
         <v>1334</v>
       </c>
       <c r="H2" t="n">
-        <v>9413</v>
+        <v>9433</v>
       </c>
       <c r="I2" t="n">
         <v>1357</v>
@@ -547,7 +547,7 @@
         <v>5086</v>
       </c>
       <c r="H3" t="n">
-        <v>402910</v>
+        <v>404442</v>
       </c>
       <c r="I3" t="n">
         <v>3609</v>
@@ -584,7 +584,7 @@
         <v>3219</v>
       </c>
       <c r="H4" t="n">
-        <v>182311</v>
+        <v>185416</v>
       </c>
       <c r="I4" t="n">
         <v>3348</v>
@@ -621,7 +621,7 @@
         <v>3097</v>
       </c>
       <c r="H5" t="n">
-        <v>171206</v>
+        <v>173984</v>
       </c>
       <c r="I5" t="n">
         <v>3424</v>
@@ -658,7 +658,7 @@
         <v>3026</v>
       </c>
       <c r="H6" t="n">
-        <v>173969</v>
+        <v>176410</v>
       </c>
       <c r="I6" t="n">
         <v>3313</v>
@@ -695,10 +695,10 @@
         <v>3391</v>
       </c>
       <c r="H7" t="n">
-        <v>139296</v>
+        <v>139301</v>
       </c>
       <c r="I7" t="n">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="J7" t="n">
         <v>4217</v>
@@ -732,7 +732,7 @@
         <v>1061</v>
       </c>
       <c r="H8" t="n">
-        <v>8336</v>
+        <v>8338</v>
       </c>
       <c r="I8" t="n">
         <v>1334</v>
@@ -769,7 +769,7 @@
         <v>1864</v>
       </c>
       <c r="H9" t="n">
-        <v>54530</v>
+        <v>54534</v>
       </c>
       <c r="I9" t="n">
         <v>2406</v>
@@ -806,7 +806,7 @@
         <v>1353</v>
       </c>
       <c r="H10" t="n">
-        <v>23804</v>
+        <v>23807</v>
       </c>
       <c r="I10" t="n">
         <v>1817</v>
@@ -843,7 +843,7 @@
         <v>2498</v>
       </c>
       <c r="H11" t="n">
-        <v>22180</v>
+        <v>22264</v>
       </c>
       <c r="I11" t="n">
         <v>4161</v>
@@ -880,7 +880,7 @@
         <v>2281</v>
       </c>
       <c r="H12" t="n">
-        <v>108944</v>
+        <v>109316</v>
       </c>
       <c r="I12" t="n">
         <v>2910</v>
@@ -917,7 +917,7 @@
         <v>992</v>
       </c>
       <c r="H13" t="n">
-        <v>5406</v>
+        <v>5408</v>
       </c>
       <c r="I13" t="n">
         <v>986</v>
@@ -954,7 +954,7 @@
         <v>4606</v>
       </c>
       <c r="H14" t="n">
-        <v>596664</v>
+        <v>596831</v>
       </c>
       <c r="I14" t="n">
         <v>3880</v>
@@ -991,7 +991,7 @@
         <v>8490</v>
       </c>
       <c r="H15" t="n">
-        <v>1898969</v>
+        <v>1909484</v>
       </c>
       <c r="I15" t="n">
         <v>7303</v>
